--- a/Metadata/Instruments.xlsx
+++ b/Metadata/Instruments.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owner\Dropbox\Scripts\Metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33EABDD-DD4B-4767-A88D-98B9E47D94F5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379DCBBC-B16D-4144-A668-83BB0A4EFEF8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14130" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14130" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4K" sheetId="1" r:id="rId1"/>
     <sheet name="1.5K" sheetId="3" r:id="rId2"/>
     <sheet name="0.3K" sheetId="2" r:id="rId3"/>
     <sheet name="Vup" sheetId="4" r:id="rId4"/>
+    <sheet name="SMS" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -58,12 +59,62 @@
         </r>
       </text>
     </comment>
+    <comment ref="A13" authorId="0" shapeId="0" xr:uid="{B17E4438-90A5-48F9-89F2-743BC1053EC3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="177"/>
+          </rPr>
+          <t>owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="177"/>
+          </rPr>
+          <t xml:space="preserve">
+the associated "serialnumber" is the actual model number of the device. The port itself is composed of this number and other stuff (see script)
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A14" authorId="0" shapeId="0" xr:uid="{A5FEB69B-6E39-4BB6-9CB1-3E5291B51945}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="177"/>
+          </rPr>
+          <t>owner:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="177"/>
+          </rPr>
+          <t xml:space="preserve">
+the associated "serialnumber" is the actual model number of the device. The port itself is composed of this number and other stuff (see script)
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="46">
   <si>
     <t>Device</t>
   </si>
@@ -143,43 +194,64 @@
     <t>GPIB7-14</t>
   </si>
   <si>
+    <t>Arduino</t>
+  </si>
+  <si>
+    <t>Serial-COM12</t>
+  </si>
+  <si>
+    <t>Serial-COM8</t>
+  </si>
+  <si>
+    <t>Serial-COM9</t>
+  </si>
+  <si>
+    <t>Magnet</t>
+  </si>
+  <si>
+    <t>TCPIP-192.168.236.2</t>
+  </si>
+  <si>
+    <t>GPIB0-18</t>
+  </si>
+  <si>
+    <t>VISA-04509845</t>
+  </si>
+  <si>
+    <t>VISA-04499542</t>
+  </si>
+  <si>
+    <t>VISA-04499369</t>
+  </si>
+  <si>
+    <t>Serial-COM7</t>
+  </si>
+  <si>
+    <t>VISA326-0</t>
+  </si>
+  <si>
+    <t>OSCILLOSCOPE</t>
+  </si>
+  <si>
+    <t>VISA200-0</t>
+  </si>
+  <si>
+    <t>MPS</t>
+  </si>
+  <si>
+    <t>Serial-COM3</t>
+  </si>
+  <si>
+    <t>SMS</t>
+  </si>
+  <si>
+    <t>TCPIP-132.64.81.133</t>
+  </si>
+  <si>
     <t>VISA-04500131</t>
   </si>
   <si>
     <t>VISA-04499955</t>
-  </si>
-  <si>
-    <t>Arduino</t>
-  </si>
-  <si>
-    <t>Serial-COM12</t>
-  </si>
-  <si>
-    <t>Serial-COM8</t>
-  </si>
-  <si>
-    <t>Serial-COM9</t>
-  </si>
-  <si>
-    <t>Magnet</t>
-  </si>
-  <si>
-    <t>TCPIP-192.168.236.2</t>
-  </si>
-  <si>
-    <t>GPIB0-18</t>
-  </si>
-  <si>
-    <t>VISA-04509845</t>
-  </si>
-  <si>
-    <t>VISA-04499542</t>
-  </si>
-  <si>
-    <t>VISA-04499369</t>
-  </si>
-  <si>
-    <t>VISA-00004326</t>
   </si>
 </sst>
 </file>
@@ -527,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.125" style="1" customWidth="1"/>
@@ -619,23 +691,31 @@
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>23</v>
+      <c r="B11" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -699,15 +779,15 @@
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -715,7 +795,7 @@
         <v>19</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -726,7 +806,7 @@
         <v>19</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -737,7 +817,7 @@
         <v>19</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -755,7 +835,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -783,7 +863,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -791,14 +871,16 @@
         <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -811,49 +893,56 @@
         <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="1">
-        <v>3</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="1">
-        <v>2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="1"/>
+        <v>7</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -881,10 +970,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -892,7 +981,7 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -900,8 +989,57 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
-      </c>
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE41A94E-1CA3-4A7B-A613-CA2C3B5B129E}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="16.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
